--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/92.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/92.xlsx
@@ -426,13 +426,13 @@
         <v>-14.91307832271587</v>
       </c>
       <c r="E2">
-        <v>-6.383438664347906</v>
+        <v>-8.373168630786124</v>
       </c>
       <c r="F2">
-        <v>-1.021536887959321</v>
+        <v>-1.649173003748255</v>
       </c>
       <c r="G2">
-        <v>-7.095721832630479</v>
+        <v>-9.458636953467446</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-13.85177259424445</v>
       </c>
       <c r="E3">
-        <v>-6.725234297024842</v>
+        <v>-8.943081613125445</v>
       </c>
       <c r="F3">
-        <v>-0.7287167908711863</v>
+        <v>-1.066301919365132</v>
       </c>
       <c r="G3">
-        <v>-7.121252759829338</v>
+        <v>-8.842312690421329</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-12.60755920000485</v>
       </c>
       <c r="E4">
-        <v>-7.407041343619691</v>
+        <v>-9.684143742110662</v>
       </c>
       <c r="F4">
-        <v>-0.724725851964279</v>
+        <v>-1.411109538686439</v>
       </c>
       <c r="G4">
-        <v>-6.269310349662212</v>
+        <v>-7.757887219758884</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-11.33748490934182</v>
       </c>
       <c r="E5">
-        <v>-8.703403069321476</v>
+        <v>-11.51126073540744</v>
       </c>
       <c r="F5">
-        <v>-0.8579020579524552</v>
+        <v>-1.177392554509548</v>
       </c>
       <c r="G5">
-        <v>-6.132326596338249</v>
+        <v>-6.993346522374057</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-10.03525359617805</v>
       </c>
       <c r="E6">
-        <v>-10.13736700622033</v>
+        <v>-11.40542576937418</v>
       </c>
       <c r="F6">
-        <v>-0.6547513897965024</v>
+        <v>-1.5298312607844</v>
       </c>
       <c r="G6">
-        <v>-5.2098993610945</v>
+        <v>-6.740808177001833</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-8.732165066472977</v>
       </c>
       <c r="E7">
-        <v>-10.28936070781378</v>
+        <v>-11.68920712153885</v>
       </c>
       <c r="F7">
-        <v>-0.5942340275027725</v>
+        <v>-1.297081129068884</v>
       </c>
       <c r="G7">
-        <v>-4.896920385811803</v>
+        <v>-6.935289485251857</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-7.430255354999421</v>
       </c>
       <c r="E8">
-        <v>-11.82983888184705</v>
+        <v>-12.42345389714252</v>
       </c>
       <c r="F8">
-        <v>-0.6843991563864866</v>
+        <v>-1.693127177725361</v>
       </c>
       <c r="G8">
-        <v>-4.877897991143151</v>
+        <v>-5.859259558077005</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-6.137558609030757</v>
       </c>
       <c r="E9">
-        <v>-12.52742313188463</v>
+        <v>-13.91570835146811</v>
       </c>
       <c r="F9">
-        <v>-0.7566842454848893</v>
+        <v>-1.20440186704441</v>
       </c>
       <c r="G9">
-        <v>-3.256651008560186</v>
+        <v>-5.697032895016099</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-4.839743645683398</v>
       </c>
       <c r="E10">
-        <v>-13.24679839884711</v>
+        <v>-14.64898150516014</v>
       </c>
       <c r="F10">
-        <v>-0.6166117920879319</v>
+        <v>-1.45514210610636</v>
       </c>
       <c r="G10">
-        <v>-1.922812347514589</v>
+        <v>-4.569467705431411</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-3.547226267781942</v>
       </c>
       <c r="E11">
-        <v>-14.60359261018125</v>
+        <v>-16.34561051992589</v>
       </c>
       <c r="F11">
-        <v>-0.7391146120590041</v>
+        <v>-1.44236635048651</v>
       </c>
       <c r="G11">
-        <v>-1.452847302759651</v>
+        <v>-3.893255673579878</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-2.267430512338029</v>
       </c>
       <c r="E12">
-        <v>-14.5694343307414</v>
+        <v>-16.89334756504966</v>
       </c>
       <c r="F12">
-        <v>-0.4873156655925823</v>
+        <v>-1.239224392713092</v>
       </c>
       <c r="G12">
-        <v>-1.516999054219649</v>
+        <v>-3.169593592513972</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-0.9998137900390984</v>
       </c>
       <c r="E13">
-        <v>-14.78630747944274</v>
+        <v>-17.25853276597621</v>
       </c>
       <c r="F13">
-        <v>-0.5973737244801313</v>
+        <v>-1.313337078437912</v>
       </c>
       <c r="G13">
-        <v>-0.5581127809519063</v>
+        <v>-3.077331998880023</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>0.2398335193997447</v>
       </c>
       <c r="E14">
-        <v>-16.56376522677141</v>
+        <v>-18.59685986030707</v>
       </c>
       <c r="F14">
-        <v>-0.9467930954271983</v>
+        <v>-1.102742200626436</v>
       </c>
       <c r="G14">
-        <v>0.550463119419522</v>
+        <v>-1.753726234096313</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>1.436724175512358</v>
       </c>
       <c r="E15">
-        <v>-17.6785894864537</v>
+        <v>-18.96217185850584</v>
       </c>
       <c r="F15">
-        <v>-0.6274744309619311</v>
+        <v>-1.19762677313816</v>
       </c>
       <c r="G15">
-        <v>1.465706470843052</v>
+        <v>-0.7203758600137442</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>2.583606508615336</v>
       </c>
       <c r="E16">
-        <v>-16.76780468013501</v>
+        <v>-19.16055071935986</v>
       </c>
       <c r="F16">
-        <v>-0.4191767185808</v>
+        <v>-1.086030935806719</v>
       </c>
       <c r="G16">
-        <v>1.850292546140186</v>
+        <v>-0.342437360159467</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>3.65741561337442</v>
       </c>
       <c r="E17">
-        <v>-20.27938720701295</v>
+        <v>-20.86705633593635</v>
       </c>
       <c r="F17">
-        <v>-0.5315747029584108</v>
+        <v>-1.175137357285962</v>
       </c>
       <c r="G17">
-        <v>1.808632641073997</v>
+        <v>0.442804178482423</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>4.629332090020732</v>
       </c>
       <c r="E18">
-        <v>-19.5415538799952</v>
+        <v>-22.19514002206186</v>
       </c>
       <c r="F18">
-        <v>-0.587454974331734</v>
+        <v>-0.9828390339155578</v>
       </c>
       <c r="G18">
-        <v>3.263845833225894</v>
+        <v>-0.4533009091785805</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>5.470146457552089</v>
       </c>
       <c r="E19">
-        <v>-21.20351742623225</v>
+        <v>-21.69122501991033</v>
       </c>
       <c r="F19">
-        <v>-0.6911718747338633</v>
+        <v>-0.9135503164091665</v>
       </c>
       <c r="G19">
-        <v>3.037947447808185</v>
+        <v>1.042665098561744</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>6.140034920052804</v>
       </c>
       <c r="E20">
-        <v>-21.33517375105725</v>
+        <v>-22.71739534394446</v>
       </c>
       <c r="F20">
-        <v>-0.2853044738427881</v>
+        <v>-0.4835915811324264</v>
       </c>
       <c r="G20">
-        <v>3.327686393405199</v>
+        <v>1.940289726625273</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>6.602738198403395</v>
       </c>
       <c r="E21">
-        <v>-21.49922225045912</v>
+        <v>-23.04750751368161</v>
       </c>
       <c r="F21">
-        <v>-0.04373626759010515</v>
+        <v>-0.3869815610258315</v>
       </c>
       <c r="G21">
-        <v>2.909415517245981</v>
+        <v>1.850040944679201</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>6.835754591627725</v>
       </c>
       <c r="E22">
-        <v>-24.11266347044778</v>
+        <v>-23.83073879262625</v>
       </c>
       <c r="F22">
-        <v>-0.08563241573009801</v>
+        <v>-0.1998936301172233</v>
       </c>
       <c r="G22">
-        <v>3.560358154996257</v>
+        <v>2.107905957824113</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>6.831127576032314</v>
       </c>
       <c r="E23">
-        <v>-22.94182651576461</v>
+        <v>-24.83068019520796</v>
       </c>
       <c r="F23">
-        <v>-0.004896671866910424</v>
+        <v>-0.5006362160473434</v>
       </c>
       <c r="G23">
-        <v>3.623642543524965</v>
+        <v>1.897275808433523</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>6.598167043615254</v>
       </c>
       <c r="E24">
-        <v>-22.92119931665967</v>
+        <v>-25.38441293991788</v>
       </c>
       <c r="F24">
-        <v>-0.2850803794557534</v>
+        <v>-0.6701964817368257</v>
       </c>
       <c r="G24">
-        <v>3.808380916252915</v>
+        <v>1.438222321776023</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>6.163459557079683</v>
       </c>
       <c r="E25">
-        <v>-22.13096701689917</v>
+        <v>-25.41718097783738</v>
       </c>
       <c r="F25">
-        <v>-0.4706891290393412</v>
+        <v>-0.5153686403257189</v>
       </c>
       <c r="G25">
-        <v>3.544686032413347</v>
+        <v>0.9853165181849495</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>5.564839295433949</v>
       </c>
       <c r="E26">
-        <v>-23.26333911336119</v>
+        <v>-25.88177976865432</v>
       </c>
       <c r="F26">
-        <v>-0.2731637842950293</v>
+        <v>-1.219916642045012</v>
       </c>
       <c r="G26">
-        <v>2.930894336704773</v>
+        <v>1.366889997041347</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>4.849437325792023</v>
       </c>
       <c r="E27">
-        <v>-23.36889784247998</v>
+        <v>-25.06075384564166</v>
       </c>
       <c r="F27">
-        <v>-0.2161123623972387</v>
+        <v>-0.5735191541288246</v>
       </c>
       <c r="G27">
-        <v>3.600938822216643</v>
+        <v>0.8572679272714793</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>4.067040749827113</v>
       </c>
       <c r="E28">
-        <v>-23.34649095309003</v>
+        <v>-25.94261981694737</v>
       </c>
       <c r="F28">
-        <v>-0.1752590846025626</v>
+        <v>-0.5723020761328094</v>
       </c>
       <c r="G28">
-        <v>3.009936922000412</v>
+        <v>0.7013875800093561</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>3.262632355356666</v>
       </c>
       <c r="E29">
-        <v>-23.62839751701553</v>
+        <v>-25.30572164708659</v>
       </c>
       <c r="F29">
-        <v>-0.4324766808586605</v>
+        <v>-0.2265165184087181</v>
       </c>
       <c r="G29">
-        <v>2.679753041550121</v>
+        <v>1.561977135125058</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>2.477696892437042</v>
       </c>
       <c r="E30">
-        <v>-22.45257924092392</v>
+        <v>-24.77965787856354</v>
       </c>
       <c r="F30">
-        <v>-0.4645182189398314</v>
+        <v>-0.3974854905099837</v>
       </c>
       <c r="G30">
-        <v>2.775209311629466</v>
+        <v>0.9406076006770921</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>1.742846313948679</v>
       </c>
       <c r="E31">
-        <v>-22.64531109469037</v>
+        <v>-25.1602580050122</v>
       </c>
       <c r="F31">
-        <v>-0.2986471961803654</v>
+        <v>-0.6034155625475327</v>
       </c>
       <c r="G31">
-        <v>3.363254894679129</v>
+        <v>0.2629455498793586</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>1.072992593479072</v>
       </c>
       <c r="E32">
-        <v>-22.49018821755762</v>
+        <v>-24.29361676332028</v>
       </c>
       <c r="F32">
-        <v>-0.3616422663788004</v>
+        <v>-0.285378116167856</v>
       </c>
       <c r="G32">
-        <v>1.819183349707655</v>
+        <v>0.5350988775717644</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>0.4795858634894706</v>
       </c>
       <c r="E33">
-        <v>-21.72997970046797</v>
+        <v>-24.29448170185574</v>
       </c>
       <c r="F33">
-        <v>-0.3594345803326778</v>
+        <v>-0.4515397489628051</v>
       </c>
       <c r="G33">
-        <v>2.116529928953914</v>
+        <v>1.193841160612563</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-0.03457083274911431</v>
       </c>
       <c r="E34">
-        <v>-21.61693087534049</v>
+        <v>-23.12033896114697</v>
       </c>
       <c r="F34">
-        <v>-0.3672644223786104</v>
+        <v>-0.4000217955335599</v>
       </c>
       <c r="G34">
-        <v>2.165261159291986</v>
+        <v>0.3620169356875882</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-0.4791384872753665</v>
       </c>
       <c r="E35">
-        <v>-20.92718088533619</v>
+        <v>-24.10102529224806</v>
       </c>
       <c r="F35">
-        <v>-0.1648478019144637</v>
+        <v>-0.7723724362832325</v>
       </c>
       <c r="G35">
-        <v>1.821163055940139</v>
+        <v>0.5481821535429642</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-0.862982935498755</v>
       </c>
       <c r="E36">
-        <v>-20.18056231874356</v>
+        <v>-23.09842567542385</v>
       </c>
       <c r="F36">
-        <v>-0.0669391429572085</v>
+        <v>-0.2402124071654384</v>
       </c>
       <c r="G36">
-        <v>2.051017543277276</v>
+        <v>0.303307721094153</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-1.197520299857526</v>
       </c>
       <c r="E37">
-        <v>-19.16360291084103</v>
+        <v>-22.67524883635508</v>
       </c>
       <c r="F37">
-        <v>-0.04704383739450044</v>
+        <v>-0.4883696218793072</v>
       </c>
       <c r="G37">
-        <v>2.846839585462677</v>
+        <v>0.994662188242312</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-1.498004812307288</v>
       </c>
       <c r="E38">
-        <v>-18.85807129801752</v>
+        <v>-21.70525423238609</v>
       </c>
       <c r="F38">
-        <v>0.131092987680044</v>
+        <v>-0.5291706373787737</v>
       </c>
       <c r="G38">
-        <v>2.530070035537514</v>
+        <v>-0.3475587741087195</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-1.77331204788586</v>
       </c>
       <c r="E39">
-        <v>-18.5913849352318</v>
+        <v>-21.61300921684985</v>
       </c>
       <c r="F39">
-        <v>0.02300426709834404</v>
+        <v>-0.01553838376570579</v>
       </c>
       <c r="G39">
-        <v>2.153240568438892</v>
+        <v>0.6872151345557361</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-2.028620391469118</v>
       </c>
       <c r="E40">
-        <v>-17.14869010044616</v>
+        <v>-19.58290790463325</v>
       </c>
       <c r="F40">
-        <v>0.3564313757113036</v>
+        <v>0.02019398095139674</v>
       </c>
       <c r="G40">
-        <v>1.87380404056009</v>
+        <v>0.02867479479283311</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-2.271244119173234</v>
       </c>
       <c r="E41">
-        <v>-17.11685945664624</v>
+        <v>-18.90245487176669</v>
       </c>
       <c r="F41">
-        <v>0.2587317659348863</v>
+        <v>0.12542015309094</v>
       </c>
       <c r="G41">
-        <v>2.130000538753209</v>
+        <v>-0.5734075013433392</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-2.506214060086716</v>
       </c>
       <c r="E42">
-        <v>-17.05030447415551</v>
+        <v>-19.56959871952471</v>
       </c>
       <c r="F42">
-        <v>0.3836536966917922</v>
+        <v>0.08782851762911151</v>
       </c>
       <c r="G42">
-        <v>1.807808315234719</v>
+        <v>0.1788543826363312</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-2.735409508621101</v>
       </c>
       <c r="E43">
-        <v>-15.51790056927791</v>
+        <v>-17.9181684038295</v>
       </c>
       <c r="F43">
-        <v>0.792534098086991</v>
+        <v>0.04850114048396142</v>
       </c>
       <c r="G43">
-        <v>1.308627706095713</v>
+        <v>-1.508232729631658</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-2.961481420411936</v>
       </c>
       <c r="E44">
-        <v>-14.5232710667072</v>
+        <v>-19.29158664324581</v>
       </c>
       <c r="F44">
-        <v>0.5974785427178069</v>
+        <v>0.1188406468652468</v>
       </c>
       <c r="G44">
-        <v>1.496587239633374</v>
+        <v>-1.402169471644488</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-3.186325755285116</v>
       </c>
       <c r="E45">
-        <v>-14.63364356369616</v>
+        <v>-16.94327399098422</v>
       </c>
       <c r="F45">
-        <v>0.4929982960644357</v>
+        <v>0.09302465673766833</v>
       </c>
       <c r="G45">
-        <v>0.2000153897233527</v>
+        <v>-1.087227342857002</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-3.4101199570979</v>
       </c>
       <c r="E46">
-        <v>-13.87640572555554</v>
+        <v>-16.61568870974336</v>
       </c>
       <c r="F46">
-        <v>0.5494748327149218</v>
+        <v>0.5890389738944301</v>
       </c>
       <c r="G46">
-        <v>0.03179332869082657</v>
+        <v>-1.796720289014828</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-3.635571434006249</v>
       </c>
       <c r="E47">
-        <v>-13.40343831477243</v>
+        <v>-16.05865470748185</v>
       </c>
       <c r="F47">
-        <v>0.6854074788489205</v>
+        <v>-0.09514415345822734</v>
       </c>
       <c r="G47">
-        <v>0.0537687299805087</v>
+        <v>-1.868377047212353</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-3.86818666681858</v>
       </c>
       <c r="E48">
-        <v>-12.63659558326154</v>
+        <v>-16.06473191960014</v>
       </c>
       <c r="F48">
-        <v>0.7951678010243668</v>
+        <v>0.4099693460356918</v>
       </c>
       <c r="G48">
-        <v>-0.1925259265046498</v>
+        <v>-2.306084136232632</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-4.11286274558107</v>
       </c>
       <c r="E49">
-        <v>-11.67255592261265</v>
+        <v>-15.74901576873338</v>
       </c>
       <c r="F49">
-        <v>1.202235650999345</v>
+        <v>0.4475879044980827</v>
       </c>
       <c r="G49">
-        <v>-0.2926500657943676</v>
+        <v>-2.125242275604404</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-4.372828325061826</v>
       </c>
       <c r="E50">
-        <v>-11.13343203505148</v>
+        <v>-14.22969462526394</v>
       </c>
       <c r="F50">
-        <v>0.7789823265685757</v>
+        <v>0.4357631642804541</v>
       </c>
       <c r="G50">
-        <v>-0.7305855824568566</v>
+        <v>-2.265467053011314</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-4.651515922295597</v>
       </c>
       <c r="E51">
-        <v>-10.87195794584859</v>
+        <v>-14.27502465008072</v>
       </c>
       <c r="F51">
-        <v>0.690022397886511</v>
+        <v>0.6869040809390108</v>
       </c>
       <c r="G51">
-        <v>-0.8545390285382484</v>
+        <v>-2.178932703160305</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-4.950680308665946</v>
       </c>
       <c r="E52">
-        <v>-10.01124900510671</v>
+        <v>-13.75477544218352</v>
       </c>
       <c r="F52">
-        <v>0.8305525422930304</v>
+        <v>0.5544991397316534</v>
       </c>
       <c r="G52">
-        <v>-1.874246644453481</v>
+        <v>-2.459249836152553</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-5.267639328688673</v>
       </c>
       <c r="E53">
-        <v>-10.17304232445276</v>
+        <v>-13.56962425390591</v>
       </c>
       <c r="F53">
-        <v>0.5498089946630795</v>
+        <v>0.6267153376227346</v>
       </c>
       <c r="G53">
-        <v>-1.711530020652763</v>
+        <v>-3.345032642822109</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-5.603889481875465</v>
       </c>
       <c r="E54">
-        <v>-8.743534405977451</v>
+        <v>-12.29352744938845</v>
       </c>
       <c r="F54">
-        <v>0.853384830475921</v>
+        <v>0.7758149147376968</v>
       </c>
       <c r="G54">
-        <v>-1.495556650761789</v>
+        <v>-3.150594371664095</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-5.957449958313394</v>
       </c>
       <c r="E55">
-        <v>-8.802626463303541</v>
+        <v>-10.86358932588241</v>
       </c>
       <c r="F55">
-        <v>0.8919227302222245</v>
+        <v>0.4595686397483821</v>
       </c>
       <c r="G55">
-        <v>-2.319501777303298</v>
+        <v>-3.571447473343944</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-6.321561943969988</v>
       </c>
       <c r="E56">
-        <v>-8.399356795972482</v>
+        <v>-11.06479848299122</v>
       </c>
       <c r="F56">
-        <v>0.832392808566771</v>
+        <v>0.628663295898725</v>
       </c>
       <c r="G56">
-        <v>-2.012349362169718</v>
+        <v>-3.010432494622431</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-6.694099432208524</v>
       </c>
       <c r="E57">
-        <v>-7.965062553214871</v>
+        <v>-11.10497963286128</v>
       </c>
       <c r="F57">
-        <v>1.248693664028761</v>
+        <v>0.1611224273956491</v>
       </c>
       <c r="G57">
-        <v>-2.087776831736472</v>
+        <v>-3.2486858359927</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-7.069418424282018</v>
       </c>
       <c r="E58">
-        <v>-7.673827332833575</v>
+        <v>-10.0098225357943</v>
       </c>
       <c r="F58">
-        <v>0.7841087826168531</v>
+        <v>0.4625024549567337</v>
       </c>
       <c r="G58">
-        <v>-2.702075040912555</v>
+        <v>-3.544824066117125</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-7.438422187788535</v>
       </c>
       <c r="E59">
-        <v>-8.098226859884425</v>
+        <v>-10.14804514793042</v>
       </c>
       <c r="F59">
-        <v>0.9833928327802606</v>
+        <v>0.5412775708966072</v>
       </c>
       <c r="G59">
-        <v>-2.395687361798546</v>
+        <v>-4.981259843970276</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-7.796511325056124</v>
       </c>
       <c r="E60">
-        <v>-6.949973405077507</v>
+        <v>-9.293173410184433</v>
       </c>
       <c r="F60">
-        <v>0.5992253703425366</v>
+        <v>0.4691096760359471</v>
       </c>
       <c r="G60">
-        <v>-2.919713615209782</v>
+        <v>-4.548220624160368</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-8.136269260216542</v>
       </c>
       <c r="E61">
-        <v>-6.671490367501811</v>
+        <v>-9.880996507224092</v>
       </c>
       <c r="F61">
-        <v>1.005906796074148</v>
+        <v>0.2866247863705636</v>
       </c>
       <c r="G61">
-        <v>-3.736921781578875</v>
+        <v>-4.800560336800237</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-8.449886713456682</v>
       </c>
       <c r="E62">
-        <v>-7.026762738825573</v>
+        <v>-9.782493140609246</v>
       </c>
       <c r="F62">
-        <v>0.9654557795819934</v>
+        <v>0.6199418274224</v>
       </c>
       <c r="G62">
-        <v>-3.660706402173774</v>
+        <v>-4.399398359987972</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-8.732567049845297</v>
       </c>
       <c r="E63">
-        <v>-6.33468058470732</v>
+        <v>-9.951862596970125</v>
       </c>
       <c r="F63">
-        <v>0.9661351894197169</v>
+        <v>0.1399055192465068</v>
       </c>
       <c r="G63">
-        <v>-3.700111825727719</v>
+        <v>-4.500287235297261</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-8.979185078826106</v>
       </c>
       <c r="E64">
-        <v>-6.096537193591951</v>
+        <v>-7.207476022575666</v>
       </c>
       <c r="F64">
-        <v>0.7927748213861379</v>
+        <v>0.3865629644584544</v>
       </c>
       <c r="G64">
-        <v>-3.881476752551151</v>
+        <v>-4.866400466485262</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-9.183544263587221</v>
       </c>
       <c r="E65">
-        <v>-5.392812332799978</v>
+        <v>-7.89147032211622</v>
       </c>
       <c r="F65">
-        <v>1.034986804093447</v>
+        <v>0.5156611277143742</v>
       </c>
       <c r="G65">
-        <v>-3.395349624473492</v>
+        <v>-5.400090202325631</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-9.340784891609831</v>
       </c>
       <c r="E66">
-        <v>-6.025951869234393</v>
+        <v>-8.477500143448841</v>
       </c>
       <c r="F66">
-        <v>0.6760493605945888</v>
+        <v>0.3577260552971753</v>
       </c>
       <c r="G66">
-        <v>-3.599226260963968</v>
+        <v>-5.304183698052944</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-9.4475564744398</v>
       </c>
       <c r="E67">
-        <v>-5.451474185095339</v>
+        <v>-7.804102473086235</v>
       </c>
       <c r="F67">
-        <v>0.7334634511470151</v>
+        <v>0.3347615276703456</v>
       </c>
       <c r="G67">
-        <v>-4.081549572217005</v>
+        <v>-5.830441259157649</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-9.50200954065104</v>
       </c>
       <c r="E68">
-        <v>-4.423451715192068</v>
+        <v>-7.375296740825922</v>
       </c>
       <c r="F68">
-        <v>0.7482631829267967</v>
+        <v>0.20331789595366</v>
       </c>
       <c r="G68">
-        <v>-4.549865965293386</v>
+        <v>-5.425809830620228</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-9.502082277161819</v>
       </c>
       <c r="E69">
-        <v>-5.423972762446757</v>
+        <v>-8.538263207683762</v>
       </c>
       <c r="F69">
-        <v>0.5502848982906691</v>
+        <v>-0.1644978029071516</v>
       </c>
       <c r="G69">
-        <v>-4.483959624697575</v>
+        <v>-6.214014307519766</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-9.446955582344469</v>
       </c>
       <c r="E70">
-        <v>-5.614884169662124</v>
+        <v>-8.154212384041253</v>
       </c>
       <c r="F70">
-        <v>0.6973438703335876</v>
+        <v>-0.02679378170673394</v>
       </c>
       <c r="G70">
-        <v>-5.000262375365692</v>
+        <v>-5.860080573370744</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-9.338712384536191</v>
       </c>
       <c r="E71">
-        <v>-4.922725031485741</v>
+        <v>-8.954162789022215</v>
       </c>
       <c r="F71">
-        <v>0.3003072136270027</v>
+        <v>0.3492730249735173</v>
       </c>
       <c r="G71">
-        <v>-4.531945982289312</v>
+        <v>-6.340450662755611</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-9.178194906650639</v>
       </c>
       <c r="E72">
-        <v>-6.260603806889848</v>
+        <v>-7.763088083998765</v>
       </c>
       <c r="F72">
-        <v>0.3952780981111177</v>
+        <v>0.1198296712094387</v>
       </c>
       <c r="G72">
-        <v>-5.448268571558644</v>
+        <v>-5.962704174542611</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-8.969308729952736</v>
       </c>
       <c r="E73">
-        <v>-6.006230364930989</v>
+        <v>-7.682897866270939</v>
       </c>
       <c r="F73">
-        <v>0.4677587748900772</v>
+        <v>-0.1667537919836951</v>
       </c>
       <c r="G73">
-        <v>-4.832152872881501</v>
+        <v>-6.404562687669137</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-8.722809797446752</v>
       </c>
       <c r="E74">
-        <v>-5.844903478407732</v>
+        <v>-8.621700341275089</v>
       </c>
       <c r="F74">
-        <v>0.4367023018883097</v>
+        <v>0.1219201630178188</v>
       </c>
       <c r="G74">
-        <v>-5.421489568691479</v>
+        <v>-6.529317285771032</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-8.448256759961968</v>
       </c>
       <c r="E75">
-        <v>-5.667763160649691</v>
+        <v>-8.645669554197687</v>
       </c>
       <c r="F75">
-        <v>0.6310404384777997</v>
+        <v>-0.04770503461419641</v>
       </c>
       <c r="G75">
-        <v>-5.011157380735433</v>
+        <v>-5.257567906314466</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-8.15634195573667</v>
       </c>
       <c r="E76">
-        <v>-5.557209524700434</v>
+        <v>-9.405121816128052</v>
       </c>
       <c r="F76">
-        <v>0.2321152124670532</v>
+        <v>-0.3674330870586047</v>
       </c>
       <c r="G76">
-        <v>-4.430289060414911</v>
+        <v>-5.979074822234307</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-7.859755264803679</v>
       </c>
       <c r="E77">
-        <v>-7.138534534282893</v>
+        <v>-9.317849065052229</v>
       </c>
       <c r="F77">
-        <v>0.371084614693907</v>
+        <v>-0.1069395951164203</v>
       </c>
       <c r="G77">
-        <v>-5.21281264116906</v>
+        <v>-5.873792852994405</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-7.566864645143076</v>
       </c>
       <c r="E78">
-        <v>-7.219118729249387</v>
+        <v>-10.31234271340271</v>
       </c>
       <c r="F78">
-        <v>0.3261936786678182</v>
+        <v>-0.4771443143506724</v>
       </c>
       <c r="G78">
-        <v>-4.570431074183339</v>
+        <v>-6.300422856640283</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-7.282272456511642</v>
       </c>
       <c r="E79">
-        <v>-7.256197874424192</v>
+        <v>-9.650927385264399</v>
       </c>
       <c r="F79">
-        <v>-0.04385346182784767</v>
+        <v>-0.1704367000900495</v>
       </c>
       <c r="G79">
-        <v>-4.945578784148011</v>
+        <v>-5.721037660721354</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-7.009277757681882</v>
       </c>
       <c r="E80">
-        <v>-8.230517171070499</v>
+        <v>-9.781809341034087</v>
       </c>
       <c r="F80">
-        <v>0.3867854751395737</v>
+        <v>-0.07137985434410071</v>
       </c>
       <c r="G80">
-        <v>-5.154679461499457</v>
+        <v>-5.546234235156756</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-6.747619300416225</v>
       </c>
       <c r="E81">
-        <v>-9.681784407152666</v>
+        <v>-11.58604395517011</v>
       </c>
       <c r="F81">
-        <v>0.1627370155764397</v>
+        <v>-0.5967093598486044</v>
       </c>
       <c r="G81">
-        <v>-4.75806948480369</v>
+        <v>-5.634172256316417</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-6.493394378113487</v>
       </c>
       <c r="E82">
-        <v>-10.22946711058833</v>
+        <v>-11.81950943263556</v>
       </c>
       <c r="F82">
-        <v>0.1435931784706076</v>
+        <v>-0.3892842694268805</v>
       </c>
       <c r="G82">
-        <v>-4.112023143905997</v>
+        <v>-5.483654992827914</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-6.242872583922249</v>
       </c>
       <c r="E83">
-        <v>-10.78271983705344</v>
+        <v>-11.74976187596942</v>
       </c>
       <c r="F83">
-        <v>0.1971287732361227</v>
+        <v>-0.5414704893710341</v>
       </c>
       <c r="G83">
-        <v>-4.205489776116241</v>
+        <v>-4.31291697886559</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-5.99371193800881</v>
       </c>
       <c r="E84">
-        <v>-10.97958618758889</v>
+        <v>-12.88270908863041</v>
       </c>
       <c r="F84">
-        <v>0.6067131319107344</v>
+        <v>-0.3915727244746905</v>
       </c>
       <c r="G84">
-        <v>-3.961231105137733</v>
+        <v>-4.751498051908237</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-5.743002014645054</v>
       </c>
       <c r="E85">
-        <v>-12.14896044516758</v>
+        <v>-13.78015301052251</v>
       </c>
       <c r="F85">
-        <v>0.3300579211014904</v>
+        <v>-0.5903389028037492</v>
       </c>
       <c r="G85">
-        <v>-4.161893201909578</v>
+        <v>-5.533240343915117</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-5.489718270725261</v>
       </c>
       <c r="E86">
-        <v>-14.69557497422505</v>
+        <v>-14.75377492217163</v>
       </c>
       <c r="F86">
-        <v>0.4826471942011235</v>
+        <v>-0.4688480709126429</v>
       </c>
       <c r="G86">
-        <v>-3.830030874870877</v>
+        <v>-4.683691458172885</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-5.238358038047774</v>
       </c>
       <c r="E87">
-        <v>-14.65396282656857</v>
+        <v>-17.34612251023257</v>
       </c>
       <c r="F87">
-        <v>-0.008755371329878636</v>
+        <v>-0.5886570071215526</v>
       </c>
       <c r="G87">
-        <v>-3.083012895025412</v>
+        <v>-4.396743302465476</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-4.992740614063878</v>
       </c>
       <c r="E88">
-        <v>-17.42441076887717</v>
+        <v>-17.96300029650544</v>
       </c>
       <c r="F88">
-        <v>0.2107106351669314</v>
+        <v>-0.4477903252080023</v>
       </c>
       <c r="G88">
-        <v>-2.651387278160774</v>
+        <v>-4.120378960847117</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-4.756073590085623</v>
       </c>
       <c r="E89">
-        <v>-18.83541534255714</v>
+        <v>-20.03353635313653</v>
       </c>
       <c r="F89">
-        <v>0.5655035202850844</v>
+        <v>-0.5053057729390167</v>
       </c>
       <c r="G89">
-        <v>-3.051903698592881</v>
+        <v>-3.930092113795349</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-4.536525107997021</v>
       </c>
       <c r="E90">
-        <v>-19.30573812451978</v>
+        <v>-20.86451133354404</v>
       </c>
       <c r="F90">
-        <v>0.3038562985835025</v>
+        <v>-0.5786147279117509</v>
       </c>
       <c r="G90">
-        <v>-2.966925305145329</v>
+        <v>-4.165266647814096</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-4.337968205953323</v>
       </c>
       <c r="E91">
-        <v>-21.71111407775202</v>
+        <v>-22.31943304815039</v>
       </c>
       <c r="F91">
-        <v>0.3698572426094415</v>
+        <v>-0.6887812706545076</v>
       </c>
       <c r="G91">
-        <v>-3.825217341656777</v>
+        <v>-3.873117625064491</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-4.162327698803277</v>
       </c>
       <c r="E92">
-        <v>-23.23308437851594</v>
+        <v>-25.02612913337901</v>
       </c>
       <c r="F92">
-        <v>0.1304381252840098</v>
+        <v>-1.07080993825343</v>
       </c>
       <c r="G92">
-        <v>-2.510281895640418</v>
+        <v>-3.171742136568958</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-4.012351344756874</v>
       </c>
       <c r="E93">
-        <v>-26.15198022726998</v>
+        <v>-27.43456180656643</v>
       </c>
       <c r="F93">
-        <v>0.1092996105776818</v>
+        <v>-0.9980798277927894</v>
       </c>
       <c r="G93">
-        <v>-2.832338386791798</v>
+        <v>-3.935326086292937</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-3.887234149150634</v>
       </c>
       <c r="E94">
-        <v>-28.08303928446482</v>
+        <v>-30.43136778638544</v>
       </c>
       <c r="F94">
-        <v>-0.1948186445111976</v>
+        <v>-1.149570008987107</v>
       </c>
       <c r="G94">
-        <v>-2.746648226053303</v>
+        <v>-3.810677425648298</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-3.781342034448226</v>
       </c>
       <c r="E95">
-        <v>-29.7057002047893</v>
+        <v>-30.73983837883993</v>
       </c>
       <c r="F95">
-        <v>-0.1083372155867957</v>
+        <v>-0.8845922537453562</v>
       </c>
       <c r="G95">
-        <v>-2.785576931049592</v>
+        <v>-3.606410144784187</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-3.690045936136797</v>
       </c>
       <c r="E96">
-        <v>-32.37958749583235</v>
+        <v>-32.83858909277581</v>
       </c>
       <c r="F96">
-        <v>0.03035662181077168</v>
+        <v>-1.042001535798629</v>
       </c>
       <c r="G96">
-        <v>-3.140957373599276</v>
+        <v>-2.972844560569546</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-3.605610681016743</v>
       </c>
       <c r="E97">
-        <v>-34.3675694713036</v>
+        <v>-34.51054924538478</v>
       </c>
       <c r="F97">
-        <v>-0.4560311389389914</v>
+        <v>-1.077189897533778</v>
       </c>
       <c r="G97">
-        <v>-2.998640331411547</v>
+        <v>-4.186864646912301</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-3.521632502373278</v>
       </c>
       <c r="E98">
-        <v>-37.79011993495374</v>
+        <v>-36.97852003058804</v>
       </c>
       <c r="F98">
-        <v>-0.387720359835384</v>
+        <v>-1.630014913289184</v>
       </c>
       <c r="G98">
-        <v>-2.734296580646282</v>
+        <v>-5.037989352331226</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-3.433181753368971</v>
       </c>
       <c r="E99">
-        <v>-39.22800553034324</v>
+        <v>-40.64979692910948</v>
       </c>
       <c r="F99">
-        <v>-0.7392745663564634</v>
+        <v>-1.474093522943466</v>
       </c>
       <c r="G99">
-        <v>-2.987828089680287</v>
+        <v>-4.927791222965507</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-3.339861147372181</v>
       </c>
       <c r="E100">
-        <v>-43.28302305203765</v>
+        <v>-43.19262338965953</v>
       </c>
       <c r="F100">
-        <v>-0.6017851373075878</v>
+        <v>-1.590578260435868</v>
       </c>
       <c r="G100">
-        <v>-3.155159613962749</v>
+        <v>-4.092573688862778</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-3.240385779003458</v>
       </c>
       <c r="E101">
-        <v>-44.3243162150204</v>
+        <v>-45.80990701984371</v>
       </c>
       <c r="F101">
-        <v>-0.806070530751953</v>
+        <v>-1.910745791271811</v>
       </c>
       <c r="G101">
-        <v>-3.879172612855819</v>
+        <v>-5.000782131015358</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-3.143793330997085</v>
       </c>
       <c r="E102">
-        <v>-46.8085396934372</v>
+        <v>-48.34175872363617</v>
       </c>
       <c r="F102">
-        <v>-1.035124292860834</v>
+        <v>-1.974338710453325</v>
       </c>
       <c r="G102">
-        <v>-3.643435286095396</v>
+        <v>-4.967597222529703</v>
       </c>
     </row>
   </sheetData>
